--- a/output/StructureDefinition-BRDiagnosticoLaboratorioClinico-3.2.1.xlsx
+++ b/output/StructureDefinition-BRDiagnosticoLaboratorioClinico-3.2.1.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6182" uniqueCount="735">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6182" uniqueCount="736">
   <si>
     <t>Property</t>
   </si>
@@ -2051,6 +2051,10 @@
   <si>
     <t xml:space="preserve">obs-3
 </t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
   </si>
   <si>
     <t>OBX-7</t>
@@ -20083,7 +20087,7 @@
         <v>655</v>
       </c>
       <c r="AJ145" t="s" s="2">
-        <v>104</v>
+        <v>656</v>
       </c>
       <c r="AK145" t="s" s="2">
         <v>83</v>
@@ -20092,10 +20096,10 @@
         <v>83</v>
       </c>
       <c r="AM145" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="AN145" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AO145" t="s" s="2">
         <v>83</v>
@@ -20106,10 +20110,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -20135,10 +20139,10 @@
         <v>652</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" s="2"/>
@@ -20189,7 +20193,7 @@
         <v>83</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>80</v>
@@ -20201,7 +20205,7 @@
         <v>655</v>
       </c>
       <c r="AJ146" t="s" s="2">
-        <v>104</v>
+        <v>656</v>
       </c>
       <c r="AK146" t="s" s="2">
         <v>83</v>
@@ -20210,10 +20214,10 @@
         <v>83</v>
       </c>
       <c r="AM146" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="AN146" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="AO146" t="s" s="2">
         <v>83</v>
@@ -20224,10 +20228,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -20253,16 +20257,16 @@
         <v>197</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="O147" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>83</v>
@@ -20290,10 +20294,10 @@
         <v>116</v>
       </c>
       <c r="Y147" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="Z147" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="AA147" t="s" s="2">
         <v>83</v>
@@ -20311,7 +20315,7 @@
         <v>83</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>80</v>
@@ -20329,10 +20333,10 @@
         <v>83</v>
       </c>
       <c r="AL147" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="AM147" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="AN147" t="s" s="2">
         <v>546</v>
@@ -20346,10 +20350,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20375,16 +20379,16 @@
         <v>197</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="O148" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>83</v>
@@ -20412,10 +20416,10 @@
         <v>591</v>
       </c>
       <c r="Y148" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="Z148" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="AA148" t="s" s="2">
         <v>83</v>
@@ -20433,7 +20437,7 @@
         <v>83</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>80</v>
@@ -20451,10 +20455,10 @@
         <v>83</v>
       </c>
       <c r="AL148" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="AM148" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="AN148" t="s" s="2">
         <v>546</v>
@@ -20468,10 +20472,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20494,17 +20498,17 @@
         <v>83</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="N149" s="2"/>
       <c r="O149" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>83</v>
@@ -20553,7 +20557,7 @@
         <v>83</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>80</v>
@@ -20577,7 +20581,7 @@
         <v>83</v>
       </c>
       <c r="AN149" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="AO149" t="s" s="2">
         <v>83</v>
@@ -20588,10 +20592,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20617,10 +20621,10 @@
         <v>206</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="N150" s="2"/>
       <c r="O150" s="2"/>
@@ -20671,7 +20675,7 @@
         <v>83</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>80</v>
@@ -20692,10 +20696,10 @@
         <v>83</v>
       </c>
       <c r="AM150" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="AN150" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="AO150" t="s" s="2">
         <v>83</v>
@@ -20706,10 +20710,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20732,16 +20736,16 @@
         <v>82</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
@@ -20791,7 +20795,7 @@
         <v>83</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>80</v>
@@ -20812,10 +20816,10 @@
         <v>83</v>
       </c>
       <c r="AM151" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="AN151" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="AO151" t="s" s="2">
         <v>83</v>
@@ -20826,10 +20830,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -20852,16 +20856,16 @@
         <v>82</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="N152" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="O152" s="2"/>
       <c r="P152" t="s" s="2">
@@ -20911,7 +20915,7 @@
         <v>83</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>80</v>
@@ -20932,10 +20936,10 @@
         <v>83</v>
       </c>
       <c r="AM152" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="AN152" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="AO152" t="s" s="2">
         <v>83</v>
@@ -20946,10 +20950,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -20975,16 +20979,16 @@
         <v>636</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="N153" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="O153" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="P153" t="s" s="2">
         <v>83</v>
@@ -21033,7 +21037,7 @@
         <v>83</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>80</v>
@@ -21054,10 +21058,10 @@
         <v>83</v>
       </c>
       <c r="AM153" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="AN153" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="AO153" t="s" s="2">
         <v>83</v>
@@ -21068,10 +21072,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21186,10 +21190,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21306,10 +21310,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21428,10 +21432,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21457,13 +21461,13 @@
         <v>197</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="O157" t="s" s="2">
         <v>278</v>
@@ -21494,10 +21498,10 @@
         <v>591</v>
       </c>
       <c r="Y157" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="Z157" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="AA157" t="s" s="2">
         <v>83</v>
@@ -21515,7 +21519,7 @@
         <v>83</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>93</v>
@@ -21533,7 +21537,7 @@
         <v>83</v>
       </c>
       <c r="AL157" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="AM157" t="s" s="2">
         <v>282</v>
@@ -21550,10 +21554,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21576,16 +21580,16 @@
         <v>82</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="M158" t="s" s="2">
         <v>521</v>
       </c>
       <c r="N158" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="O158" t="s" s="2">
         <v>509</v>
@@ -21637,7 +21641,7 @@
         <v>83</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>80</v>
@@ -21655,7 +21659,7 @@
         <v>83</v>
       </c>
       <c r="AL158" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="AM158" t="s" s="2">
         <v>514</v>
@@ -21672,10 +21676,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21701,13 +21705,13 @@
         <v>197</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="O159" t="s" s="2">
         <v>531</v>
@@ -21759,7 +21763,7 @@
         <v>83</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>80</v>
@@ -21794,10 +21798,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21823,10 +21827,10 @@
         <v>197</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="N160" t="s" s="2">
         <v>540</v>
@@ -21860,10 +21864,10 @@
         <v>320</v>
       </c>
       <c r="Y160" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="Z160" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="AA160" t="s" s="2">
         <v>83</v>
@@ -21881,7 +21885,7 @@
         <v>83</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>80</v>
@@ -21916,10 +21920,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -21945,10 +21949,10 @@
         <v>83</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="N161" t="s" s="2">
         <v>639</v>
@@ -22003,7 +22007,7 @@
         <v>83</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>80</v>
